--- a/results/tables/excel/table_9_rule_comparison.xlsx
+++ b/results/tables/excel/table_9_rule_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,50 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>equal_weights</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>lambda_star</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>minimum_ratio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>guarantee_kept</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>total_net_delivery</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>weighted_satisfaction</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>temporal_variation</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>users_better_than_three_stage</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>users_worse_than_three_stage</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>total_delivery_relative_to_three_stage</t>
         </is>
@@ -511,34 +516,37 @@
           <t>Three-stage lexicographic (proposed)</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.7806122448979592</v>
+      <c r="D2" t="b">
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
+        <v>0.7806122448979592</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>74.15306122448979</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.823922902494331</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -558,34 +566,37 @@
           <t>Total-delivery maximization</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.59375</v>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>75.05</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.8338888888888889</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
         <v>1.012095775423146</v>
       </c>
     </row>
@@ -605,34 +616,37 @@
           <t>Equal proportional allocation</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0.7806122448979592</v>
+      <c r="D4" t="b">
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4" t="n">
+        <v>0.7806122448979592</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>70.25510204081633</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.947433603963121</v>
       </c>
     </row>
@@ -652,34 +666,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,1,1)</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.7806122448979591</v>
       </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>74.15306122448979</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.823922902494331</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -699,34 +716,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,5,1)</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.7806122448979591</v>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>74.15306122448979</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.823922902494331</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -746,34 +766,37 @@
           <t>Weighted single objective (35), (a,b,c) = (5,1,1)</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.7806122448979591</v>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>74.15306122448979</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.823922902494331</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -793,34 +816,37 @@
           <t>Full leximin (progressive filling)</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.7806122448979592</v>
+      <c r="D8" t="b">
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0.7806122448979592</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F8" t="n">
+        <v>0.7806122448979592</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>74.15306122448979</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.8239229024943312</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -840,34 +866,37 @@
           <t>Three-stage lexicographic (proposed)</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0.72</v>
+      <c r="D9" t="b">
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0.72</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>72</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.72</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -887,34 +916,37 @@
           <t>Total-delivery maximization</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0.72</v>
+      <c r="D10" t="b">
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0.72</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>72</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0.72</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -934,34 +966,37 @@
           <t>Equal proportional allocation</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0.72</v>
+      <c r="D11" t="b">
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0.72</v>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>72</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.72</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -981,34 +1016,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,1,1)</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0.72</v>
+      <c r="D12" t="b">
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0.72</v>
       </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="F12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>72</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>0.72</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1028,34 +1066,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,5,1)</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0.72</v>
+      <c r="D13" t="b">
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0.72</v>
       </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="F13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>72</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.72</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1075,34 +1116,37 @@
           <t>Weighted single objective (35), (a,b,c) = (5,1,1)</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0.72</v>
+      <c r="D14" t="b">
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0.72</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>72</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>0.72</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1122,34 +1166,37 @@
           <t>Full leximin (progressive filling)</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0.72</v>
+      <c r="D15" t="b">
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0.72</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="F15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>72</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.72</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1169,34 +1216,37 @@
           <t>Three-stage lexicographic (proposed)</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0.8499999999996504</v>
+      <c r="D16" t="b">
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0.8499999999996504</v>
       </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="F16" t="n">
+        <v>0.8499999999996504</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>5918844.757203277</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.9020152785693699</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5.417942221248455</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>20</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1216,34 +1266,37 @@
           <t>Total-delivery maximization</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.8499999999996504</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>6119889.104413168</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.9326538711144148</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>6.596582926667205</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>20</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>17</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>1.033966822151437</v>
       </c>
     </row>
@@ -1263,34 +1316,37 @@
           <t>Equal proportional allocation</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0.8499999999996504</v>
+      <c r="D18" t="b">
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0.8499999999996504</v>
       </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F18" t="n">
+        <v>0.8499999999996504</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
         <v>5577530.850253556</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.8499999999996496</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>20</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>20</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>0.9423343708188426</v>
       </c>
     </row>
@@ -1310,34 +1366,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,1,1)</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.8499999999996504</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.8499999999901662</v>
       </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>5907243.907456269</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0.9002473417260427</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>3.443568132760208</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>20</v>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
       <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
         <v>14</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.9980400145259952</v>
       </c>
     </row>
@@ -1357,34 +1416,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,5,1)</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.8499999999996504</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.8114035721359634</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>5983822.20764218</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.9119176590950703</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>4.565290029007024</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>20</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>15</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1.01097806296741</v>
       </c>
     </row>
@@ -1404,34 +1466,37 @@
           <t>Weighted single objective (35), (a,b,c) = (5,1,1)</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.8499999999996504</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.8499999999923679</v>
       </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
         <v>5907243.907456312</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.9002473417260486</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3.443568132782043</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>20</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
       <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
         <v>14</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0.9980400145260024</v>
       </c>
     </row>
@@ -1451,34 +1516,37 @@
           <t>Full leximin (progressive filling)</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>0.8499999999996504</v>
+      <c r="D22" t="b">
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0.8499999999996504</v>
       </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="F22" t="n">
+        <v>0.8499999999996504</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
         <v>5917909.294352056</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0.9018727166643107</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>4.800000000006674</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>20</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>7</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>10</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>0.9998419517845804</v>
       </c>
     </row>
@@ -1498,34 +1566,37 @@
           <t>Three-stage lexicographic (proposed)</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0.7</v>
+      <c r="D23" t="b">
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0.7</v>
       </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="F23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
         <v>110</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1545,34 +1616,37 @@
           <t>Total-delivery maximization</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0.7</v>
+      <c r="D24" t="b">
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0.7</v>
       </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
         <v>110</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1592,34 +1666,37 @@
           <t>Equal proportional allocation</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0.7</v>
+      <c r="D25" t="b">
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0.7</v>
       </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
         <v>98</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0.7</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
         <v>0.8909090909090909</v>
       </c>
     </row>
@@ -1639,34 +1716,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,1,1)</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0.7</v>
+      <c r="D26" t="b">
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0.7</v>
       </c>
-      <c r="F26" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="F26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
         <v>110</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1686,34 +1766,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,5,1)</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0.7</v>
+      <c r="D27" t="b">
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0.7</v>
       </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="F27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
         <v>110</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1733,34 +1816,37 @@
           <t>Weighted single objective (35), (a,b,c) = (5,1,1)</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0.7</v>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0.7</v>
       </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
         <v>110</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1780,34 +1866,37 @@
           <t>Full leximin (progressive filling)</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0.7</v>
+      <c r="D29" t="b">
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0.7</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
         <v>110</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1827,34 +1916,37 @@
           <t>Three-stage lexicographic (proposed)</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0.6</v>
+      <c r="D30" t="b">
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0.6</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="F30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
         <v>22</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>0.4000000000000011</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1874,34 +1966,37 @@
           <t>Total-delivery maximization</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
         <v>0.6</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>22</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>3.75</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
       <c r="L31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1921,34 +2016,37 @@
           <t>Equal proportional allocation</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0.6</v>
+      <c r="D32" t="b">
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
         <v>18</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>0.6</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>0.8181818181818182</v>
       </c>
     </row>
@@ -1968,34 +2066,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,1,1)</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>0.6</v>
+      <c r="D33" t="b">
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0.6</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="F33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
         <v>22</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>0.4000000000000002</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2015,34 +2116,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,5,1)</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0.6</v>
+      <c r="D34" t="b">
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0.6</v>
       </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
         <v>22</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>0.4000000000000002</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2062,34 +2166,37 @@
           <t>Weighted single objective (35), (a,b,c) = (5,1,1)</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0.6</v>
+      <c r="D35" t="b">
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0.6</v>
       </c>
-      <c r="F35" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="F35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
         <v>22</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>0.4000000000000002</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2109,34 +2216,37 @@
           <t>Full leximin (progressive filling)</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0.6</v>
+      <c r="D36" t="b">
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0.6</v>
       </c>
-      <c r="F36" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
         <v>22</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>0.4000000000000001</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2156,34 +2266,37 @@
           <t>Three-stage lexicographic (proposed)</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0.75</v>
+      <c r="D37" t="b">
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0.75</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
         <v>75</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>0.75</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>2</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2203,34 +2316,37 @@
           <t>Total-delivery maximization</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.75</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>0.375</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>75</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0.75</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>2</v>
       </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2250,34 +2366,37 @@
           <t>Equal proportional allocation</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>0.75</v>
+      <c r="D39" t="b">
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>0.75</v>
       </c>
-      <c r="F39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
         <v>75</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>0.75</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>2</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2297,34 +2416,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,1,1)</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>0.75</v>
+      <c r="D40" t="b">
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0.75</v>
       </c>
-      <c r="F40" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="F40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
         <v>75</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>0.75</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>2</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2344,34 +2466,37 @@
           <t>Weighted single objective (35), (a,b,c) = (1,5,1)</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>0.75</v>
+      <c r="D41" t="b">
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0.75</v>
       </c>
-      <c r="F41" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
         <v>75</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>0.75</v>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2391,34 +2516,37 @@
           <t>Weighted single objective (35), (a,b,c) = (5,1,1)</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>0.75</v>
+      <c r="D42" t="b">
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0.75</v>
       </c>
-      <c r="F42" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
         <v>75</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>0.75</v>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>2</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2438,34 +2566,37 @@
           <t>Full leximin (progressive filling)</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>0.75</v>
+      <c r="D43" t="b">
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0.75</v>
       </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
         <v>75</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>0.75</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>2</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
         <v>1</v>
       </c>
     </row>
